--- a/docs/files/REPORT_FILTRI/Agente - CR D'AMBROSIO RAFFAELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR D'AMBROSIO RAFFAELLO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>151</v>
+        <v>206</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -817,28 +817,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>151</v>
+        <v>206</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>222</v>
+        <v>321</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>192</v>
+        <v>257</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - CR D'AMBROSIO RAFFAELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR D'AMBROSIO RAFFAELLO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -817,28 +817,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
